--- a/artfynd/A 14774-2023 artfynd.xlsx
+++ b/artfynd/A 14774-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 14774-2023 artfynd.xlsx
+++ b/artfynd/A 14774-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>123110</v>
       </c>
       <c r="B2" t="n">
-        <v>93235</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -729,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>621977.4154794195</v>
+        <v>621977</v>
       </c>
       <c r="R2" t="n">
-        <v>6684012.610849352</v>
+        <v>6684013</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -762,19 +757,9 @@
           <t>2011-04-30</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2011-04-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -815,15 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>746863</v>
+        <v>746861</v>
       </c>
       <c r="B3" t="n">
-        <v>93158</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96458</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -860,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>621973.5206498173</v>
+        <v>622013</v>
       </c>
       <c r="R3" t="n">
-        <v>6684084.465109959</v>
+        <v>6684013</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -893,19 +873,9 @@
           <t>2011-04-30</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2011-04-30</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -946,15 +916,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>746861</v>
+        <v>746862</v>
       </c>
       <c r="B4" t="n">
-        <v>93158</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96458</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -991,10 +956,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>622012.7155524071</v>
+        <v>621974</v>
       </c>
       <c r="R4" t="n">
-        <v>6684012.798666404</v>
+        <v>6684024</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1024,19 +989,9 @@
           <t>2011-04-30</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2011-04-30</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1077,15 +1032,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>746864</v>
+        <v>746863</v>
       </c>
       <c r="B5" t="n">
-        <v>93158</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96458</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,10 +1072,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>621985.4573456144</v>
+        <v>621974</v>
       </c>
       <c r="R5" t="n">
-        <v>6684099.26106355</v>
+        <v>6684084</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1155,19 +1105,9 @@
           <t>2011-04-30</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2011-04-30</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1208,15 +1148,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>746862</v>
+        <v>746864</v>
       </c>
       <c r="B6" t="n">
-        <v>93158</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96458</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,10 +1188,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>621973.5404496721</v>
+        <v>621985</v>
       </c>
       <c r="R6" t="n">
-        <v>6684024.396033837</v>
+        <v>6684099</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1286,19 +1221,9 @@
           <t>2011-04-30</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2011-04-30</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1332,6 +1257,319 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3933322</v>
+      </c>
+      <c r="B7" t="n">
+        <v>102241</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Korbovallen, 1,2 km S-ut, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>621961</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6683983</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Östervåla</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2011-04-30</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2011-04-30</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>4949788</v>
+      </c>
+      <c r="B8" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Korbovallen, 1,0 km S-ut, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>622124</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6684128</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Östervåla</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2011-04-30</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2011-04-30</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>4949789</v>
+      </c>
+      <c r="B9" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Korbovallen, 1,2 km S-ut, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>621961</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6683983</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Östervåla</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2011-04-30</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2011-04-30</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>

--- a/artfynd/A 14774-2023 artfynd.xlsx
+++ b/artfynd/A 14774-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -797,6 +802,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123110</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -913,6 +923,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/746861</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1029,6 +1044,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/746862</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1145,6 +1165,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/746863</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1261,6 +1286,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/746864</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1367,6 +1397,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3933322</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1468,6 +1503,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4949788</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1574,8 +1614,23 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4949789</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>